--- a/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Forecast_Series_h2.xlsx
+++ b/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Forecast_Series_h2.xlsx
@@ -459,22 +459,22 @@
         <v>0.2999999999999829</v>
       </c>
       <c r="D2">
-        <v>0.5380264176829421</v>
+        <v>0.3893550854202221</v>
       </c>
       <c r="E2">
         <v>0.7957634757526395</v>
       </c>
       <c r="F2">
-        <v>1.033789893435599</v>
+        <v>0.8851185611728787</v>
       </c>
       <c r="G2">
-        <v>-0.2380264176829592</v>
+        <v>-0.08935508542023923</v>
       </c>
       <c r="H2">
-        <v>0.2380264176829592</v>
+        <v>0.08935508542023918</v>
       </c>
       <c r="I2">
-        <v>0.4354820344276649</v>
+        <v>0.1501953579908254</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -497,22 +497,22 @@
         <v>0.3599999999999994</v>
       </c>
       <c r="D3">
-        <v>0.542262457156433</v>
+        <v>0.4636469815305221</v>
       </c>
       <c r="E3">
         <v>2.467941123023811</v>
       </c>
       <c r="F3">
-        <v>2.650203580180245</v>
+        <v>2.571588104554334</v>
       </c>
       <c r="G3">
-        <v>-0.1822624571564336</v>
+        <v>-0.1036469815305227</v>
       </c>
       <c r="H3">
-        <v>0.1822624571564333</v>
+        <v>0.1036469815305225</v>
       </c>
       <c r="I3">
-        <v>0.9328456296881553</v>
+        <v>0.5223319927733208</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -535,25 +535,25 @@
         <v>-0.4000000000000057</v>
       </c>
       <c r="D4">
-        <v>0.5308617751097854</v>
+        <v>0.3138893366100468</v>
       </c>
       <c r="E4">
         <v>-0.7175214086404351</v>
       </c>
       <c r="F4">
-        <v>0.213340366469356</v>
+        <v>-0.003632072030382572</v>
       </c>
       <c r="G4">
-        <v>-0.9308617751097911</v>
+        <v>-0.7138893366100525</v>
       </c>
       <c r="H4">
-        <v>-0.5041810421710791</v>
+        <v>-0.7138893366100525</v>
       </c>
       <c r="I4">
-        <v>-0.4693228598920752</v>
+        <v>-0.5148237799101204</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
@@ -573,28 +573,28 @@
         <v>-0.2999999999999972</v>
       </c>
       <c r="D5">
-        <v>0.403261927397673</v>
+        <v>-3.39129626163989</v>
       </c>
       <c r="E5">
         <v>-0.3095084149472304</v>
       </c>
       <c r="F5">
-        <v>0.3937535124504399</v>
+        <v>-3.400804676587123</v>
       </c>
       <c r="G5">
-        <v>-0.7032619273976702</v>
+        <v>3.091296261639893</v>
       </c>
       <c r="H5">
-        <v>0.08424509750320952</v>
+        <v>3.091296261639893</v>
       </c>
       <c r="I5">
-        <v>0.05924636964391179</v>
+        <v>11.4696769893737</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
@@ -611,22 +611,22 @@
         <v>0.2000000000000028</v>
       </c>
       <c r="D6">
-        <v>0.4884753284686293</v>
+        <v>0.2862907290847205</v>
       </c>
       <c r="E6">
         <v>-1.982091798344624</v>
       </c>
       <c r="F6">
-        <v>-1.693616469875998</v>
+        <v>-1.895801069259907</v>
       </c>
       <c r="G6">
-        <v>-0.2884753284686265</v>
+        <v>-0.08629072908471769</v>
       </c>
       <c r="H6">
-        <v>-0.2884753284686266</v>
+        <v>-0.08629072908471769</v>
       </c>
       <c r="I6">
-        <v>-1.060351150029791</v>
+        <v>-0.3346262028580216</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -649,28 +649,28 @@
         <v>0.2999999999999829</v>
       </c>
       <c r="D7">
-        <v>0.4792194076570963</v>
+        <v>0.2081776456234988</v>
       </c>
       <c r="E7">
         <v>-0.06479708162335629</v>
       </c>
       <c r="F7">
-        <v>0.1144223260337571</v>
+        <v>-0.1566194359998404</v>
       </c>
       <c r="G7">
-        <v>-0.1792194076571134</v>
+        <v>0.09182235437648409</v>
       </c>
       <c r="H7">
-        <v>0.04962524441040084</v>
+        <v>0.09182235437648409</v>
       </c>
       <c r="I7">
-        <v>0.008893806908071516</v>
+        <v>0.0203309859460042</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
@@ -687,31 +687,31 @@
         <v>0.4</v>
       </c>
       <c r="D8">
-        <v>0.5067148107832196</v>
+        <v>0.3580795182285995</v>
       </c>
       <c r="E8">
         <v>0.280777696258258</v>
       </c>
       <c r="F8">
-        <v>0.3874925070414775</v>
+        <v>0.2388572144868575</v>
       </c>
       <c r="G8">
-        <v>-0.1067148107832195</v>
+        <v>0.04192048177140051</v>
       </c>
       <c r="H8">
-        <v>0.1067148107832195</v>
+        <v>-0.04192048177140048</v>
       </c>
       <c r="I8">
-        <v>0.07131432829719492</v>
+        <v>-0.02178334580367393</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -725,22 +725,22 @@
         <v>0.6</v>
       </c>
       <c r="D9">
-        <v>0.5129575063459948</v>
+        <v>0.4232001440849967</v>
       </c>
       <c r="E9">
         <v>0.7818677821223996</v>
       </c>
       <c r="F9">
-        <v>0.6948252884683944</v>
+        <v>0.6050679262073962</v>
       </c>
       <c r="G9">
-        <v>0.08704249365400518</v>
+        <v>0.1767998559150033</v>
       </c>
       <c r="H9">
-        <v>-0.08704249365400518</v>
+        <v>-0.1767998559150034</v>
       </c>
       <c r="I9">
-        <v>-0.1285350472258126</v>
+        <v>-0.2452100333960811</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
@@ -763,22 +763,22 @@
         <v>0.2</v>
       </c>
       <c r="D10">
-        <v>0.4982669585733387</v>
+        <v>0.3241036406112104</v>
       </c>
       <c r="E10">
         <v>-0.0707092582566427</v>
       </c>
       <c r="F10">
-        <v>0.227557700316696</v>
+        <v>0.05339438235456767</v>
       </c>
       <c r="G10">
-        <v>-0.2982669585733387</v>
+        <v>-0.1241036406112104</v>
       </c>
       <c r="H10">
-        <v>0.1568484420600533</v>
+        <v>-0.01731487590207503</v>
       </c>
       <c r="I10">
-        <v>0.04678270777021862</v>
+        <v>-0.002148839136178827</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
@@ -787,7 +787,7 @@
         <v>1</v>
       </c>
       <c r="L10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -801,31 +801,31 @@
         <v>0.3</v>
       </c>
       <c r="D11">
-        <v>0.4933476375941009</v>
+        <v>0.2946425695029543</v>
       </c>
       <c r="E11">
         <v>0.8925127928898435</v>
       </c>
       <c r="F11">
-        <v>1.085860430483944</v>
+        <v>0.8871553623927978</v>
       </c>
       <c r="G11">
-        <v>-0.1933476375941009</v>
+        <v>0.005357430497045679</v>
       </c>
       <c r="H11">
-        <v>0.1933476375941008</v>
+        <v>-0.005357430497045734</v>
       </c>
       <c r="I11">
-        <v>0.3825137890187482</v>
+        <v>-0.00953444844973228</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -839,31 +839,31 @@
         <v>0.3</v>
       </c>
       <c r="D12">
-        <v>0.4911946000669394</v>
+        <v>0.2886970031025137</v>
       </c>
       <c r="E12">
         <v>-0.4214356569573426</v>
       </c>
       <c r="F12">
-        <v>-0.2302410568904032</v>
+        <v>-0.4327386538548288</v>
       </c>
       <c r="G12">
-        <v>-0.1911946000669394</v>
+        <v>0.01130299689748626</v>
       </c>
       <c r="H12">
-        <v>-0.1911946000669394</v>
+        <v>0.01130299689748626</v>
       </c>
       <c r="I12">
-        <v>-0.1245970686770571</v>
+        <v>0.00965472958502242</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
       </c>
       <c r="K12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -877,28 +877,28 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="D13">
-        <v>0.4757086472911365</v>
+        <v>0.2118333940613151</v>
       </c>
       <c r="E13">
         <v>0.0162427487728688</v>
       </c>
       <c r="F13">
-        <v>0.0919513960639996</v>
+        <v>-0.1719238571658218</v>
       </c>
       <c r="G13">
-        <v>-0.0757086472911308</v>
+        <v>0.1881666059386906</v>
       </c>
       <c r="H13">
-        <v>0.0757086472911308</v>
+        <v>0.155681108392953</v>
       </c>
       <c r="I13">
-        <v>0.008191232350419991</v>
+        <v>0.02929398577507536</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="b">
         <v>1</v>
@@ -915,22 +915,22 @@
         <v>0.5</v>
       </c>
       <c r="D14">
-        <v>0.4856561882341516</v>
+        <v>0.2897649239239772</v>
       </c>
       <c r="E14">
         <v>0.6608782057348365</v>
       </c>
       <c r="F14">
-        <v>0.646534393968988</v>
+        <v>0.4506431296588137</v>
       </c>
       <c r="G14">
-        <v>0.01434381176584842</v>
+        <v>0.2102350760760228</v>
       </c>
       <c r="H14">
-        <v>-0.01434381176584842</v>
+        <v>-0.2102350760760228</v>
       </c>
       <c r="I14">
-        <v>-0.0187532802304502</v>
+        <v>-0.2336807725066064</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
@@ -953,31 +953,31 @@
         <v>0.4499999999999886</v>
       </c>
       <c r="D15">
-        <v>0.4918383581678285</v>
+        <v>0.3712887134776663</v>
       </c>
       <c r="E15">
         <v>-0.2496974281391897</v>
       </c>
       <c r="F15">
-        <v>-0.2078590699713497</v>
+        <v>-0.3284087146615119</v>
       </c>
       <c r="G15">
-        <v>-0.04183835816783993</v>
+        <v>0.07871128652232229</v>
       </c>
       <c r="H15">
-        <v>-0.04183835816783993</v>
+        <v>0.07871128652232229</v>
       </c>
       <c r="I15">
-        <v>-0.01914341264997133</v>
+        <v>0.04550347824630058</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
       </c>
       <c r="K15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -991,28 +991,28 @@
         <v>0.4200000000000017</v>
       </c>
       <c r="D16">
-        <v>0.4688399666105595</v>
+        <v>0.2412251075864097</v>
       </c>
       <c r="E16">
         <v>-0.0186374241717191</v>
       </c>
       <c r="F16">
-        <v>0.03020254243883869</v>
+        <v>-0.1974123165853111</v>
       </c>
       <c r="G16">
-        <v>-0.04883996661055778</v>
+        <v>0.178774892413592</v>
       </c>
       <c r="H16">
-        <v>0.01156511826711959</v>
+        <v>0.178774892413592</v>
       </c>
       <c r="I16">
-        <v>0.0005648399900132727</v>
+        <v>0.03862426915982252</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="b">
         <v>1</v>
@@ -1029,31 +1029,31 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="D17">
-        <v>0.4762114559751854</v>
+        <v>0.331828834122106</v>
       </c>
       <c r="E17">
         <v>0.131307328824251</v>
       </c>
       <c r="F17">
-        <v>0.2075187847994307</v>
+        <v>0.06313616294635133</v>
       </c>
       <c r="G17">
-        <v>-0.0762114559751797</v>
+        <v>0.06817116587789968</v>
       </c>
       <c r="H17">
-        <v>0.0762114559751797</v>
+        <v>-0.06817116587789968</v>
       </c>
       <c r="I17">
-        <v>0.02582243144167245</v>
+        <v>-0.01325543953137175</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1067,28 +1067,28 @@
         <v>0.4490000000000123</v>
       </c>
       <c r="D18">
-        <v>0.4769657872032477</v>
+        <v>0.3212511232582483</v>
       </c>
       <c r="E18">
         <v>0.03774063242552606</v>
       </c>
       <c r="F18">
-        <v>0.0657064196287615</v>
+        <v>-0.09000824431623794</v>
       </c>
       <c r="G18">
-        <v>-0.02796578720323545</v>
+        <v>0.127748876741764</v>
       </c>
       <c r="H18">
-        <v>0.02796578720323545</v>
+        <v>0.05226761189071188</v>
       </c>
       <c r="I18">
-        <v>0.002892978244552226</v>
+        <v>0.00667712870901291</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="b">
         <v>1</v>
@@ -1105,28 +1105,28 @@
         <v>0.4399999999999977</v>
       </c>
       <c r="D19">
-        <v>0.4811495656472151</v>
+        <v>0.3799623770391106</v>
       </c>
       <c r="E19">
         <v>0.01307657371241594</v>
       </c>
       <c r="F19">
-        <v>0.05422613935963333</v>
+        <v>-0.04696104924847117</v>
       </c>
       <c r="G19">
-        <v>-0.04114956564721739</v>
+        <v>0.0600376229608871</v>
       </c>
       <c r="H19">
-        <v>0.04114956564721739</v>
+        <v>0.03388447553605523</v>
       </c>
       <c r="I19">
-        <v>0.002769477409794127</v>
+        <v>0.002034343366461087</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="b">
         <v>1</v>
@@ -1143,31 +1143,31 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="D20">
-        <v>0.4755442970578639</v>
+        <v>0.3456323769169372</v>
       </c>
       <c r="E20">
         <v>-0.2164567140176819</v>
       </c>
       <c r="F20">
-        <v>-0.1409124169598236</v>
+        <v>-0.2708243371007503</v>
       </c>
       <c r="G20">
-        <v>-0.0755442970578582</v>
+        <v>0.05436762308306847</v>
       </c>
       <c r="H20">
-        <v>-0.0755442970578582</v>
+        <v>0.05436762308306847</v>
       </c>
       <c r="I20">
-        <v>-0.02699719978987331</v>
+        <v>0.02649231252272834</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
       </c>
       <c r="K20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1181,22 +1181,22 @@
         <v>0.4999999999999858</v>
       </c>
       <c r="D21">
-        <v>0.4820643396534485</v>
+        <v>0.4113051556852885</v>
       </c>
       <c r="E21">
         <v>-0.1069669247009271</v>
       </c>
       <c r="F21">
-        <v>-0.1249025850474643</v>
+        <v>-0.1956617690156243</v>
       </c>
       <c r="G21">
-        <v>0.01793566034653726</v>
+        <v>0.08869484431469726</v>
       </c>
       <c r="H21">
-        <v>0.01793566034653726</v>
+        <v>0.08869484431469726</v>
       </c>
       <c r="I21">
-        <v>0.00415873277156526</v>
+        <v>0.02684160487434973</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -1219,25 +1219,25 @@
         <v>0.4999999999999858</v>
       </c>
       <c r="D22">
-        <v>0.4928005090967671</v>
+        <v>0.4391274312279916</v>
       </c>
       <c r="E22">
         <v>0.04841511072513038</v>
       </c>
       <c r="F22">
-        <v>0.04121561982191169</v>
+        <v>-0.01245745804686382</v>
       </c>
       <c r="G22">
-        <v>0.007199490903218697</v>
+        <v>0.06087256877199421</v>
       </c>
       <c r="H22">
-        <v>-0.007199490903218697</v>
+        <v>-0.03595765267826656</v>
       </c>
       <c r="I22">
-        <v>-0.0006452956292222756</v>
+        <v>-0.002188834685537263</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
@@ -1257,22 +1257,22 @@
         <v>0.5490000000000066</v>
       </c>
       <c r="D23">
-        <v>0.4903726392967697</v>
+        <v>0.4238537155235792</v>
       </c>
       <c r="E23">
         <v>0.7478415319443343</v>
       </c>
       <c r="F23">
-        <v>0.6892141712410975</v>
+        <v>0.6226952474679071</v>
       </c>
       <c r="G23">
-        <v>0.05862736070323687</v>
+        <v>0.1251462844764274</v>
       </c>
       <c r="H23">
-        <v>-0.05862736070323682</v>
+        <v>-0.1251462844764273</v>
       </c>
       <c r="I23">
-        <v>-0.08425078306129591</v>
+        <v>-0.1715175856817308</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
@@ -1295,31 +1295,31 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="D24">
-        <v>0.4844303646457702</v>
+        <v>0.3668028415346226</v>
       </c>
       <c r="E24">
         <v>0.3826764833261244</v>
       </c>
       <c r="F24">
-        <v>0.4671068479718888</v>
+        <v>0.3494793248607413</v>
       </c>
       <c r="G24">
-        <v>-0.08443036464576453</v>
+        <v>0.03319715846538307</v>
       </c>
       <c r="H24">
-        <v>0.08443036464576448</v>
+        <v>-0.03319715846538307</v>
       </c>
       <c r="I24">
-        <v>0.07174751653138373</v>
+        <v>-0.02430549238572999</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
       </c>
       <c r="K24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1333,25 +1333,25 @@
         <v>0.5490000000000066</v>
       </c>
       <c r="D25">
-        <v>0.4875174109176865</v>
+        <v>0.3590117854112294</v>
       </c>
       <c r="E25">
         <v>0.1246473542911689</v>
       </c>
       <c r="F25">
-        <v>0.06316476520884884</v>
+        <v>-0.06534086029760827</v>
       </c>
       <c r="G25">
-        <v>0.06148258908232007</v>
+        <v>0.1899882145887772</v>
       </c>
       <c r="H25">
-        <v>-0.06148258908232007</v>
+        <v>-0.05930649399356064</v>
       </c>
       <c r="I25">
-        <v>-0.01154717536789918</v>
+        <v>-0.01126753490735662</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
@@ -1371,31 +1371,31 @@
         <v>0.4</v>
       </c>
       <c r="D26">
-        <v>0.4755162453855642</v>
+        <v>0.2808809732270754</v>
       </c>
       <c r="E26">
         <v>0.4746895714685821</v>
       </c>
       <c r="F26">
-        <v>0.5502058168541463</v>
+        <v>0.3555705446956575</v>
       </c>
       <c r="G26">
-        <v>-0.07551624538556417</v>
+        <v>0.1191190267729246</v>
       </c>
       <c r="H26">
-        <v>0.07551624538556412</v>
+        <v>-0.1191190267729246</v>
       </c>
       <c r="I26">
-        <v>0.07739625163911218</v>
+        <v>-0.09889977700585958</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
       </c>
       <c r="K26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1409,31 +1409,31 @@
         <v>0.3500000000000085</v>
       </c>
       <c r="D27">
-        <v>0.4732134501260093</v>
+        <v>0.2801538139453355</v>
       </c>
       <c r="E27">
         <v>0.2658406583130781</v>
       </c>
       <c r="F27">
-        <v>0.3890541084390788</v>
+        <v>0.1959944722584051</v>
       </c>
       <c r="G27">
-        <v>-0.1232134501260008</v>
+        <v>0.06984618605467302</v>
       </c>
       <c r="H27">
-        <v>0.1232134501260008</v>
+        <v>-0.06984618605467302</v>
       </c>
       <c r="I27">
-        <v>0.08069184368099577</v>
+        <v>-0.03225742245648002</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -1447,22 +1447,22 @@
         <v>0.3</v>
       </c>
       <c r="D28">
-        <v>0.4794514438930083</v>
+        <v>0.3254374528737733</v>
       </c>
       <c r="E28">
         <v>0.2720044792833136</v>
       </c>
       <c r="F28">
-        <v>0.4514559231763219</v>
+        <v>0.2974419321570869</v>
       </c>
       <c r="G28">
-        <v>-0.1794514438930083</v>
+        <v>-0.0254374528737733</v>
       </c>
       <c r="H28">
-        <v>0.1794514438930083</v>
+        <v>0.0254374528737733</v>
       </c>
       <c r="I28">
-        <v>0.1298260138207985</v>
+        <v>0.01448526625515452</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
@@ -1485,22 +1485,22 @@
         <v>0.25</v>
       </c>
       <c r="D29">
-        <v>0.4694960777968994</v>
+        <v>0.2665719521681545</v>
       </c>
       <c r="E29">
         <v>2.471807318894706</v>
       </c>
       <c r="F29">
-        <v>2.691303396691605</v>
+        <v>2.48837927106286</v>
       </c>
       <c r="G29">
-        <v>-0.2194960777968994</v>
+        <v>-0.01657195216815449</v>
       </c>
       <c r="H29">
-        <v>0.2194960777968995</v>
+        <v>0.01657195216815444</v>
       </c>
       <c r="I29">
-        <v>1.133282551302338</v>
+        <v>0.0821999749138973</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
@@ -1523,31 +1523,31 @@
         <v>0.289999999999992</v>
       </c>
       <c r="D30">
-        <v>0.4636932727805407</v>
+        <v>0.2654078332331393</v>
       </c>
       <c r="E30">
         <v>9.980957649751991</v>
       </c>
       <c r="F30">
-        <v>10.15465092253254</v>
+        <v>9.956365482985138</v>
       </c>
       <c r="G30">
-        <v>-0.1736932727805487</v>
+        <v>0.02459216676685266</v>
       </c>
       <c r="H30">
-        <v>0.1736932727805485</v>
+        <v>-0.02459216676685294</v>
       </c>
       <c r="I30">
-        <v>3.497419752348165</v>
+        <v>-0.4903019753649005</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
       </c>
       <c r="K30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -1561,22 +1561,22 @@
         <v>1.999999999999957</v>
       </c>
       <c r="D31">
-        <v>0.4649655010251456</v>
+        <v>0.2570134399543461</v>
       </c>
       <c r="E31">
         <v>-6.480304150385512</v>
       </c>
       <c r="F31">
-        <v>-8.015338649360324</v>
+        <v>-8.223290710431124</v>
       </c>
       <c r="G31">
-        <v>1.535034498974811</v>
+        <v>1.742986560045611</v>
       </c>
       <c r="H31">
-        <v>1.535034498974811</v>
+        <v>1.742986560045612</v>
       </c>
       <c r="I31">
-        <v>22.25131178242568</v>
+        <v>25.62816822675912</v>
       </c>
       <c r="J31" t="b">
         <v>0</v>
@@ -1599,25 +1599,25 @@
         <v>3.8</v>
       </c>
       <c r="D32">
-        <v>0.4092359723681839</v>
+        <v>-0.05011853135311716</v>
       </c>
       <c r="E32">
         <v>3.459367396593679</v>
       </c>
       <c r="F32">
-        <v>0.06860336896186336</v>
+        <v>-0.3907511347594377</v>
       </c>
       <c r="G32">
-        <v>3.390764027631816</v>
+        <v>3.850118531353117</v>
       </c>
       <c r="H32">
-        <v>-3.390764027631816</v>
+        <v>-3.068616261834241</v>
       </c>
       <c r="I32">
-        <v>-11.96251636238241</v>
+        <v>-11.81453633529954</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
@@ -1637,25 +1637,25 @@
         <v>1.35673533549307</v>
       </c>
       <c r="D33">
-        <v>-0.2020519152164938</v>
+        <v>-4.576544413464426</v>
       </c>
       <c r="E33">
         <v>3.163673203886142</v>
       </c>
       <c r="F33">
-        <v>1.604885953176578</v>
+        <v>-2.769606545071355</v>
       </c>
       <c r="G33">
-        <v>1.558787250709564</v>
+        <v>5.933279748957497</v>
       </c>
       <c r="H33">
-        <v>-1.558787250709564</v>
+        <v>-0.3940666588147872</v>
       </c>
       <c r="I33">
-        <v>-7.433169218283712</v>
+        <v>-2.338107726485119</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
@@ -1675,22 +1675,22 @@
         <v>2.600000000000009</v>
       </c>
       <c r="D34">
-        <v>0.1923834189113169</v>
+        <v>-1.378103130372411</v>
       </c>
       <c r="E34">
         <v>0.966907881869751</v>
       </c>
       <c r="F34">
-        <v>-1.440708699218941</v>
+        <v>-3.011195248502669</v>
       </c>
       <c r="G34">
-        <v>2.407616581088692</v>
+        <v>3.97810313037242</v>
       </c>
       <c r="H34">
-        <v>0.4738008173491901</v>
+        <v>2.044287366632918</v>
       </c>
       <c r="I34">
-        <v>1.140730703983285</v>
+        <v>8.132385972583201</v>
       </c>
       <c r="J34" t="b">
         <v>0</v>
@@ -1713,22 +1713,22 @@
         <v>1.84899999999999</v>
       </c>
       <c r="D35">
-        <v>0.4530716620994173</v>
+        <v>0.3179053543475561</v>
       </c>
       <c r="E35">
         <v>0.1547337034555309</v>
       </c>
       <c r="F35">
-        <v>-1.241194634445042</v>
+        <v>-1.376360942196903</v>
       </c>
       <c r="G35">
-        <v>1.395928337900573</v>
+        <v>1.531094645652434</v>
       </c>
       <c r="H35">
-        <v>1.086460930989511</v>
+        <v>1.221627238741372</v>
       </c>
       <c r="I35">
-        <v>1.516621601590097</v>
+        <v>1.870426924220082</v>
       </c>
       <c r="J35" t="b">
         <v>0</v>
@@ -1751,22 +1751,22 @@
         <v>1.500392903354637</v>
       </c>
       <c r="D36">
-        <v>0.4182295876772667</v>
+        <v>0.09491088760332561</v>
       </c>
       <c r="E36">
         <v>1.847582543966432</v>
       </c>
       <c r="F36">
-        <v>0.7654192282890622</v>
+        <v>0.442100528215121</v>
       </c>
       <c r="G36">
-        <v>1.08216331567737</v>
+        <v>1.405482015751311</v>
       </c>
       <c r="H36">
-        <v>-1.08216331567737</v>
+        <v>-1.405482015751311</v>
       </c>
       <c r="I36">
-        <v>-2.827694661734851</v>
+        <v>-3.218108379721385</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
@@ -1789,22 +1789,22 @@
         <v>1.66</v>
       </c>
       <c r="D37">
-        <v>0.4661045680167242</v>
+        <v>0.4759850485143884</v>
       </c>
       <c r="E37">
         <v>1.424595103578154</v>
       </c>
       <c r="F37">
-        <v>0.2306996715948786</v>
+        <v>0.2405801520925428</v>
       </c>
       <c r="G37">
-        <v>1.193895431983276</v>
+        <v>1.184014951485612</v>
       </c>
       <c r="H37">
-        <v>-1.193895431983276</v>
+        <v>-1.184014951485612</v>
       </c>
       <c r="I37">
-        <v>-1.976248870664868</v>
+        <v>-1.971592399557981</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
@@ -1827,22 +1827,22 @@
         <v>2.34</v>
       </c>
       <c r="D38">
-        <v>0.4888727816645488</v>
+        <v>0.6959984776213567</v>
       </c>
       <c r="E38">
         <v>2.200270144387512</v>
       </c>
       <c r="F38">
-        <v>0.349142926052061</v>
+        <v>0.5562686220088688</v>
       </c>
       <c r="G38">
-        <v>1.851127218335451</v>
+        <v>1.644001522378643</v>
       </c>
       <c r="H38">
-        <v>-1.851127218335451</v>
+        <v>-1.644001522378643</v>
       </c>
       <c r="I38">
-        <v>-4.719287925470848</v>
+        <v>-4.531753928451397</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
@@ -1865,25 +1865,25 @@
         <v>1.096664146006177</v>
       </c>
       <c r="D39">
-        <v>0.450091724674024</v>
+        <v>0.31974861626763</v>
       </c>
       <c r="E39">
         <v>0.6965152533949663</v>
       </c>
       <c r="F39">
-        <v>0.04994283206281336</v>
+        <v>-0.0804002763435806</v>
       </c>
       <c r="G39">
-        <v>0.6465724213321531</v>
+        <v>0.7769155297385471</v>
       </c>
       <c r="H39">
-        <v>-0.646572421332153</v>
+        <v>-0.6161149770513857</v>
       </c>
       <c r="I39">
-        <v>-0.4826392117373998</v>
+        <v>-0.47866929377573</v>
       </c>
       <c r="J39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="b">
         <v>0</v>
@@ -1903,22 +1903,22 @@
         <v>1.4</v>
       </c>
       <c r="D40">
-        <v>0.4526074903095803</v>
+        <v>0.3342137259028355</v>
       </c>
       <c r="E40">
         <v>1.835306103547281</v>
       </c>
       <c r="F40">
-        <v>0.887913593856861</v>
+        <v>0.7695198294501161</v>
       </c>
       <c r="G40">
-        <v>0.9473925096904197</v>
+        <v>1.065786274097164</v>
       </c>
       <c r="H40">
-        <v>-0.9473925096904197</v>
+        <v>-1.065786274097165</v>
       </c>
       <c r="I40">
-        <v>-2.579957943562095</v>
+        <v>-2.776187725800966</v>
       </c>
       <c r="J40" t="b">
         <v>1</v>
@@ -1941,22 +1941,22 @@
         <v>-0.4</v>
       </c>
       <c r="D41">
-        <v>0.4569117622075328</v>
+        <v>0.3409475460132365</v>
       </c>
       <c r="E41">
         <v>-0.06477325635534092</v>
       </c>
       <c r="F41">
-        <v>0.7921385058521919</v>
+        <v>0.6761742896578956</v>
       </c>
       <c r="G41">
-        <v>-0.8569117622075328</v>
+        <v>-0.7409475460132365</v>
       </c>
       <c r="H41">
-        <v>0.727365249496851</v>
+        <v>0.6114010333025547</v>
       </c>
       <c r="I41">
-        <v>0.6232878377148684</v>
+        <v>0.453016095255485</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
@@ -1979,22 +1979,22 @@
         <v>0.06953162841598726</v>
       </c>
       <c r="D42">
-        <v>0.4588666317807112</v>
+        <v>0.3553890248851115</v>
       </c>
       <c r="E42">
         <v>0.05097186598095012</v>
       </c>
       <c r="F42">
-        <v>0.440306869345674</v>
+        <v>0.3368292624500743</v>
       </c>
       <c r="G42">
-        <v>-0.3893350033647239</v>
+        <v>-0.2858573964691242</v>
       </c>
       <c r="H42">
-        <v>0.3893350033647239</v>
+        <v>0.2858573964691242</v>
       </c>
       <c r="I42">
-        <v>0.1912720080714085</v>
+        <v>0.1108558209210811</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
@@ -2017,22 +2017,22 @@
         <v>0.4553446893433346</v>
       </c>
       <c r="D43">
-        <v>0.4443889302419745</v>
+        <v>0.1755723340877904</v>
       </c>
       <c r="E43">
         <v>0.5849623173407428</v>
       </c>
       <c r="F43">
-        <v>0.5740065582393827</v>
+        <v>0.3051899620851986</v>
       </c>
       <c r="G43">
-        <v>0.0109557591013601</v>
+        <v>0.2797723552555442</v>
       </c>
       <c r="H43">
-        <v>-0.01095575910136004</v>
+        <v>-0.2797723552555442</v>
       </c>
       <c r="I43">
-        <v>-0.01269738380683</v>
+        <v>-0.2490399997510869</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
@@ -2055,31 +2055,31 @@
         <v>0.42</v>
       </c>
       <c r="D44">
-        <v>0.440404459656563</v>
+        <v>0.1318607832594023</v>
       </c>
       <c r="E44">
         <v>0.7070636170015632</v>
       </c>
       <c r="F44">
-        <v>0.7274680766581262</v>
+        <v>0.4189244002609654</v>
       </c>
       <c r="G44">
-        <v>-0.02040445965656301</v>
+        <v>0.2881392167405977</v>
       </c>
       <c r="H44">
-        <v>0.02040445965656301</v>
+        <v>-0.2881392167405977</v>
       </c>
       <c r="I44">
-        <v>0.02927084406934016</v>
+        <v>-0.3244413053533236</v>
       </c>
       <c r="J44" t="b">
         <v>1</v>
       </c>
       <c r="K44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2093,22 +2093,22 @@
         <v>0.48</v>
       </c>
       <c r="D45">
-        <v>0.4468261669621719</v>
+        <v>0.219194857889999</v>
       </c>
       <c r="E45">
         <v>0.2664041604754924</v>
       </c>
       <c r="F45">
-        <v>0.2332303274376643</v>
+        <v>0.005599018365491398</v>
       </c>
       <c r="G45">
-        <v>0.03317383303782806</v>
+        <v>0.2608051421100009</v>
       </c>
       <c r="H45">
-        <v>-0.03317383303782806</v>
+        <v>-0.2608051421100009</v>
       </c>
       <c r="I45">
-        <v>-0.01657479108197178</v>
+        <v>-0.07093982771199478</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
@@ -2131,31 +2131,31 @@
         <v>0.4002364482404346</v>
       </c>
       <c r="D46">
-        <v>0.4438112397742334</v>
+        <v>0.1821935163855133</v>
       </c>
       <c r="E46">
         <v>0.4669984892513961</v>
       </c>
       <c r="F46">
-        <v>0.5105732807851949</v>
+        <v>0.2489555573964748</v>
       </c>
       <c r="G46">
-        <v>-0.04357479153379884</v>
+        <v>0.2180429318549213</v>
       </c>
       <c r="H46">
-        <v>0.04357479153379878</v>
+        <v>-0.2180429318549213</v>
       </c>
       <c r="I46">
-        <v>0.04259748608867112</v>
+        <v>-0.1561087194044969</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
       </c>
       <c r="K46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2169,22 +2169,22 @@
         <v>0.5113565490928664</v>
       </c>
       <c r="D47">
-        <v>0.4390214691225346</v>
+        <v>0.1411038934307159</v>
       </c>
       <c r="E47">
         <v>0.4061437322588163</v>
       </c>
       <c r="F47">
-        <v>0.3338086522884845</v>
+        <v>0.03589107659666579</v>
       </c>
       <c r="G47">
-        <v>0.07233507997033184</v>
+        <v>0.3702526556621505</v>
       </c>
       <c r="H47">
-        <v>-0.07233507997033184</v>
+        <v>-0.3702526556621505</v>
       </c>
       <c r="I47">
-        <v>-0.05352451491046675</v>
+        <v>-0.1636645618738534</v>
       </c>
       <c r="J47" t="b">
         <v>1</v>
@@ -2207,22 +2207,22 @@
         <v>0.52</v>
       </c>
       <c r="D48">
-        <v>0.4430508141140873</v>
+        <v>0.2234432542019461</v>
       </c>
       <c r="E48">
         <v>0.7206497229122815</v>
       </c>
       <c r="F48">
-        <v>0.6437005370263686</v>
+        <v>0.4240929771142275</v>
       </c>
       <c r="G48">
-        <v>0.07694918588591271</v>
+        <v>0.2965567457980539</v>
       </c>
       <c r="H48">
-        <v>-0.07694918588591282</v>
+        <v>-0.296556745798054</v>
       </c>
       <c r="I48">
-        <v>-0.1049856417655127</v>
+        <v>-0.3394811698959394</v>
       </c>
       <c r="J48" t="b">
         <v>1</v>
@@ -2245,31 +2245,31 @@
         <v>0.313</v>
       </c>
       <c r="D49">
-        <v>0.4448866959717733</v>
+        <v>0.2064811908043919</v>
       </c>
       <c r="E49">
         <v>-0.09868022977500479</v>
       </c>
       <c r="F49">
-        <v>0.03320646619676854</v>
+        <v>-0.2051990389706129</v>
       </c>
       <c r="G49">
-        <v>-0.1318866959717733</v>
+        <v>0.1065188091956081</v>
       </c>
       <c r="H49">
-        <v>-0.06547376357823625</v>
+        <v>0.1065188091956081</v>
       </c>
       <c r="I49">
-        <v>-0.008635118351170611</v>
+        <v>0.03236885784601537</v>
       </c>
       <c r="J49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -2283,22 +2283,22 @@
         <v>0.15047372915447</v>
       </c>
       <c r="D50">
-        <v>0.4431495669667695</v>
+        <v>0.2085679007350822</v>
       </c>
       <c r="E50">
         <v>0.4271648845785767</v>
       </c>
       <c r="F50">
-        <v>0.7198407223908763</v>
+        <v>0.4852590561591889</v>
       </c>
       <c r="G50">
-        <v>-0.2926758378122995</v>
+        <v>-0.0580941715806122</v>
       </c>
       <c r="H50">
-        <v>0.2926758378122996</v>
+        <v>0.0580941715806122</v>
       </c>
       <c r="I50">
-        <v>0.3357008269951898</v>
+        <v>0.0530065129674781</v>
       </c>
       <c r="J50" t="b">
         <v>1</v>
@@ -2321,22 +2321,22 @@
         <v>0.1461563307127136</v>
       </c>
       <c r="D51">
-        <v>0.438407812899944</v>
+        <v>0.1751453671933744</v>
       </c>
       <c r="E51">
         <v>0.1461563307127136</v>
       </c>
       <c r="F51">
-        <v>0.438407812899944</v>
+        <v>0.1751453671933744</v>
       </c>
       <c r="G51">
-        <v>-0.2922514821872304</v>
+        <v>-0.02898903648066078</v>
       </c>
       <c r="H51">
-        <v>0.2922514821872304</v>
+        <v>0.02898903648066078</v>
       </c>
       <c r="I51">
-        <v>0.1708397374043082</v>
+        <v>0.009314226641897835</v>
       </c>
       <c r="J51" t="b">
         <v>1</v>
